--- a/notebooks/evaluation_results/results_summary_metrics.xlsx
+++ b/notebooks/evaluation_results/results_summary_metrics.xlsx
@@ -497,37 +497,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0288</v>
+        <v>0.03933054393305439</v>
       </c>
       <c r="C2" t="n">
-        <v>0.241</v>
+        <v>0.2121438533572425</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1327</v>
+        <v>0.1221297910877767</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9111</v>
+        <v>0.9111111111111112</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3794</v>
+        <v>0.3482758620689656</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0477</v>
+        <v>0.05677132014422005</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4076</v>
+        <v>0.3339353425086363</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2457</v>
+        <v>0.2030036049780526</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="L2" t="n">
-        <v>1714</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3">
@@ -537,37 +537,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0045</v>
+        <v>0.01087866108786611</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0365</v>
+        <v>0.05338712891014146</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0169</v>
+        <v>0.03190402956514576</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8911</v>
+        <v>0.8932589493258951</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8625</v>
+        <v>0.8839633530515077</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0207</v>
+        <v>0.03245308691157376</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1778</v>
+        <v>0.1748020390420093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0859</v>
+        <v>0.1212729112044384</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0408</v>
+        <v>0.04531361459768923</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0408</v>
+        <v>0.03585501898303012</v>
       </c>
       <c r="L3" t="n">
-        <v>1714</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
@@ -577,37 +577,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0116</v>
+        <v>0.009205020920502092</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0954</v>
+        <v>0.04839609483960948</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0461</v>
+        <v>0.02185877989046233</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0565</v>
+        <v>0.002324500232450023</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7402</v>
+        <v>0.7398138796710432</v>
       </c>
       <c r="G4" t="n">
-        <v>0.032</v>
+        <v>0.03032246181086768</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2782</v>
+        <v>0.169983681946059</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1411</v>
+        <v>0.07306855196949787</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1633</v>
+        <v>0.03586064300451304</v>
       </c>
       <c r="K4" t="n">
-        <v>0.058</v>
+        <v>0.05548039926902774</v>
       </c>
       <c r="L4" t="n">
-        <v>1714</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5">
@@ -617,37 +617,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0067</v>
+        <v>0.01506276150627615</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0536</v>
+        <v>0.08117154811715481</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0244</v>
+        <v>0.04286179821743207</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5425383542538352</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8793</v>
+        <v>0.8300389554176886</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0256</v>
+        <v>0.0391207795364211</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2141</v>
+        <v>0.228330964060176</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1041</v>
+        <v>0.1264317792758242</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1375</v>
+        <v>0.1738405935151939</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0409</v>
+        <v>0.04867258690902811</v>
       </c>
       <c r="L5" t="n">
-        <v>1714</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6">
@@ -657,37 +657,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0064</v>
+        <v>0.005857740585774058</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0536</v>
+        <v>0.03421000199242877</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0241</v>
+        <v>0.01867243333445252</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5411</v>
+        <v>0.596001859600186</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8573</v>
+        <v>0.8413793103448277</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0244</v>
+        <v>0.0234832053563218</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2149</v>
+        <v>0.158115803058042</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1055</v>
+        <v>0.09352549446722755</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1466</v>
+        <v>0.1679480486011371</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0442</v>
+        <v>0.04705306700294522</v>
       </c>
       <c r="L6" t="n">
-        <v>1714</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7">
@@ -697,37 +697,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0067</v>
+        <v>0.01506276150627615</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0536</v>
+        <v>0.08117154811715481</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0244</v>
+        <v>0.04286179821743207</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5425383542538352</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8793</v>
+        <v>0.8300389554176886</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0256</v>
+        <v>0.0391207795364211</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2141</v>
+        <v>0.228330964060176</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1041</v>
+        <v>0.1264317792758242</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1375</v>
+        <v>0.1738405935151939</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0409</v>
+        <v>0.04867258690902811</v>
       </c>
       <c r="L7" t="n">
-        <v>1714</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8">
@@ -737,37 +737,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0062</v>
+        <v>0.01338912133891213</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0495</v>
+        <v>0.07249452082088065</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0229</v>
+        <v>0.03865619742019014</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6569</v>
+        <v>0.6401673640167362</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8883</v>
+        <v>0.8362862501803492</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0249</v>
+        <v>0.03526082205552364</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2052</v>
+        <v>0.2168159431945219</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1018</v>
+        <v>0.1187634256850726</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1502</v>
+        <v>0.1597504798225423</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0404</v>
+        <v>0.04623449703534301</v>
       </c>
       <c r="L8" t="n">
-        <v>1714</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9">
@@ -777,37 +777,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0052</v>
+        <v>0.01255230125523013</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0427</v>
+        <v>0.06503287507471608</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0201</v>
+        <v>0.03535638362114624</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7468</v>
+        <v>0.7652254765225477</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8988</v>
+        <v>0.8464290867118742</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0224</v>
+        <v>0.03313110107921197</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1925</v>
+        <v>0.1995829022278604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.1128609768751773</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1536</v>
+        <v>0.1234249999216543</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0398</v>
+        <v>0.04538812921875844</v>
       </c>
       <c r="L9" t="n">
-        <v>1714</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -817,37 +817,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.005</v>
+        <v>0.008786610878661089</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0402</v>
+        <v>0.04083482765491134</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0188</v>
+        <v>0.02596995487808776</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9265</v>
+        <v>0.9380753138075313</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9144</v>
+        <v>0.8705742317125956</v>
       </c>
       <c r="G10" t="n">
-        <v>0.022</v>
+        <v>0.02975127838431996</v>
       </c>
       <c r="H10" t="n">
-        <v>0.186</v>
+        <v>0.1536317168534246</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0941</v>
+        <v>0.1059135334952405</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0927</v>
+        <v>0.06593613620912561</v>
       </c>
       <c r="K10" t="n">
-        <v>0.039</v>
+        <v>0.043809245112667</v>
       </c>
       <c r="L10" t="n">
-        <v>1714</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -857,37 +857,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0048</v>
+        <v>0.007531380753138076</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0414</v>
+        <v>0.03849372384937238</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0155</v>
+        <v>0.02027729832253797</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9776</v>
+        <v>0.9777777777777777</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8631654883855143</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0215</v>
+        <v>0.02638970214430374</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1907</v>
+        <v>0.1502326100730752</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0806</v>
+        <v>0.09171107691050971</v>
       </c>
       <c r="J11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0207</v>
+        <v>0.01559811980970403</v>
       </c>
       <c r="L11" t="n">
-        <v>1714</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12">
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0065</v>
+        <v>0.01464435146443515</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0516</v>
+        <v>0.08047419804741981</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0237</v>
+        <v>0.0427315305302429</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.5481171548117154</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8818</v>
+        <v>0.8305583609868706</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0253</v>
+        <v>0.03764760461657571</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2095</v>
+        <v>0.2278136909541261</v>
       </c>
       <c r="I12" t="n">
-        <v>0.103</v>
+        <v>0.1261739336070604</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1484</v>
+        <v>0.173966715538455</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0414</v>
+        <v>0.04794128527062438</v>
       </c>
       <c r="L12" t="n">
-        <v>1714</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
